--- a/Collections/EURO/Cyprus/#EURO#Cyprus#Commemorative#[2009-present]#UNC.xlsx
+++ b/Collections/EURO/Cyprus/#EURO#Cyprus#Commemorative#[2009-present]#UNC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Cyprus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5B0037-14C3-4D85-ABB3-40B9BFAB5A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516F0DAD-0D45-46FC-ADD2-69089ABEAAB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3830" yWindow="1090" windowWidth="33150" windowHeight="17560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2€" sheetId="1" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="44">
   <si>
     <t>Year</t>
   </si>
@@ -545,6 +545,9 @@
     <xf numFmtId="3" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -571,9 +574,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -581,7 +581,15 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="28">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -804,9 +812,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="2" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="3" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1089,27 +1097,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="33"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="28" t="s">
+      <c r="D1" s="34"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="29"/>
-      <c r="H1" s="30" t="s">
+      <c r="G1" s="30"/>
+      <c r="H1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="31"/>
+      <c r="I1" s="32"/>
       <c r="J1" s="3"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
+      <c r="A2" s="28"/>
       <c r="B2" s="24" t="s">
         <v>34</v>
       </c>
@@ -1646,14 +1654,47 @@
       <c r="G18" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="26">
         <v>1</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>4</v>
       </c>
       <c r="J18" s="10" t="str">
-        <f t="shared" ref="J18" si="5">IF(OR(AND(H18&gt;1,H18&lt;&gt;"-"),AND(I18&gt;1,I18&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="J18:J19" si="5">IF(OR(AND(H18&gt;1,H18&lt;&gt;"-"),AND(I18&gt;1,I18&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="6">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="J19" s="10" t="str">
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -1674,11 +1715,45 @@
     <mergeCell ref="C1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="H6:I6 H3:H5 H11:I11">
-    <cfRule type="containsText" dxfId="26" priority="63" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="67" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:I6 H3:H5 H11:I11">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3">
+    <cfRule type="containsText" dxfId="26" priority="65" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3">
+    <cfRule type="colorScale" priority="66">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:I5">
+    <cfRule type="containsText" dxfId="25" priority="63" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:I5">
     <cfRule type="colorScale" priority="64">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1690,12 +1765,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3">
-    <cfRule type="containsText" dxfId="25" priority="61" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3">
+  <conditionalFormatting sqref="H7">
+    <cfRule type="containsText" dxfId="24" priority="61" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7">
     <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1707,12 +1782,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I5">
-    <cfRule type="containsText" dxfId="24" priority="59" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I5">
+  <conditionalFormatting sqref="I7">
+    <cfRule type="containsText" dxfId="23" priority="59" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7">
     <cfRule type="colorScale" priority="60">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1724,12 +1799,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7">
-    <cfRule type="containsText" dxfId="23" priority="57" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7">
+  <conditionalFormatting sqref="H8">
+    <cfRule type="containsText" dxfId="22" priority="57" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H8">
     <cfRule type="colorScale" priority="58">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1741,12 +1816,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="22" priority="55" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I7))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7">
+  <conditionalFormatting sqref="I8">
+    <cfRule type="containsText" dxfId="21" priority="55" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I8">
     <cfRule type="colorScale" priority="56">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1758,46 +1833,46 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8">
-    <cfRule type="containsText" dxfId="21" priority="53" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H8">
-    <cfRule type="colorScale" priority="54">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I8">
-    <cfRule type="containsText" dxfId="20" priority="51" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I8))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I8">
-    <cfRule type="colorScale" priority="52">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H9:I9">
-    <cfRule type="containsText" dxfId="19" priority="45" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="49" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H9))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:I9">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="containsText" dxfId="19" priority="47" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I10">
+    <cfRule type="containsText" dxfId="18" priority="45" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I10))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I10">
     <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1809,12 +1884,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
-    <cfRule type="containsText" dxfId="18" priority="43" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
+  <conditionalFormatting sqref="H12">
+    <cfRule type="containsText" dxfId="17" priority="43" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
     <cfRule type="colorScale" priority="44">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1826,12 +1901,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I10">
-    <cfRule type="containsText" dxfId="17" priority="41" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I10))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I10">
+  <conditionalFormatting sqref="I12">
+    <cfRule type="containsText" dxfId="16" priority="41" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I12">
     <cfRule type="colorScale" priority="42">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1843,12 +1918,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
-    <cfRule type="containsText" dxfId="16" priority="39" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H12">
+  <conditionalFormatting sqref="H13">
+    <cfRule type="containsText" dxfId="15" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
     <cfRule type="colorScale" priority="40">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1860,12 +1935,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I12">
-    <cfRule type="containsText" dxfId="15" priority="37" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I12))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I12">
+  <conditionalFormatting sqref="I13">
+    <cfRule type="containsText" dxfId="14" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I13">
     <cfRule type="colorScale" priority="38">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1877,46 +1952,46 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="containsText" dxfId="14" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="13" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I13))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I13">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H14:I14">
-    <cfRule type="containsText" dxfId="12" priority="27" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="13" priority="31" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H14))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:I14">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="containsText" dxfId="12" priority="29" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I15">
+    <cfRule type="containsText" dxfId="11" priority="27" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I15))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I15">
     <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1928,12 +2003,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
-    <cfRule type="containsText" dxfId="11" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15">
+  <conditionalFormatting sqref="I16">
+    <cfRule type="containsText" dxfId="10" priority="25" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I16">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1945,29 +2020,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I15">
-    <cfRule type="containsText" dxfId="10" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I15))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I15">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I16">
+  <conditionalFormatting sqref="I17">
     <cfRule type="containsText" dxfId="9" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I16">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I17))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I17">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1979,12 +2037,12 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I17">
+  <conditionalFormatting sqref="H16">
     <cfRule type="containsText" dxfId="8" priority="17" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I17))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I17">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1996,30 +2054,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="containsText" dxfId="7" priority="13" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H16))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="containsText" dxfId="6" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(H17))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -2031,11 +2072,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18">
+    <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I18">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
     <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(I18))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I18">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H18))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2047,12 +2105,29 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H18">
+  <conditionalFormatting sqref="H19">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(H19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I19">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(H18))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H18">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(I19))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I19">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
